--- a/data/trans_orig/P04D$aparatos-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257465</t>
+          <t>257484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298191</t>
+          <t>296457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>256924</t>
+          <t>258253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>295936</t>
+          <t>296512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>525118</t>
+          <t>524961</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>585706</t>
+          <t>582917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44256</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121752</t>
+          <t>121597</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>160056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102417</t>
+          <t>100485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>137454</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231875</t>
+          <t>234333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287148</t>
+          <t>288904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>27971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>26955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400118</t>
+          <t>402898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454888</t>
+          <t>454072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365588</t>
+          <t>367068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>411946</t>
+          <t>414577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782067</t>
+          <t>781386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851099</t>
+          <t>854100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41108</t>
+          <t>40046</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>29519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64110</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173034</t>
+          <t>174644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222391</t>
+          <t>221788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>160664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207509</t>
+          <t>206308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348074</t>
+          <t>348118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413933</t>
+          <t>413974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>29315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>41891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71286</t>
+          <t>73923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>397842</t>
+          <t>396541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>449627</t>
+          <t>451725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>403427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>458022</t>
+          <t>455886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>818964</t>
+          <t>818895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>892425</t>
+          <t>891389</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28581</t>
+          <t>28352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13571</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29008</t>
+          <t>28774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53210</t>
+          <t>54426</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188064</t>
+          <t>184796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237024</t>
+          <t>236222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205483</t>
+          <t>205906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258782</t>
+          <t>256618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>405578</t>
+          <t>404738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475294</t>
+          <t>475742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>42249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19296</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>73980</t>
+          <t>74739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>349590</t>
+          <t>352675</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402274</t>
+          <t>402728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375349</t>
+          <t>371745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>425490</t>
+          <t>423294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>737591</t>
+          <t>738142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>809762</t>
+          <t>811931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32735</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57490</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165552</t>
+          <t>166915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215228</t>
+          <t>214815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151862</t>
+          <t>153066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201808</t>
+          <t>203566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>332886</t>
+          <t>333757</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>404891</t>
+          <t>401860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36465</t>
+          <t>36782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68703</t>
+          <t>69486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245719</t>
+          <t>248049</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287511</t>
+          <t>291275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267981</t>
+          <t>266072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309652</t>
+          <t>308935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526209</t>
+          <t>528999</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>588692</t>
+          <t>588715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32510</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113863</t>
+          <t>112080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153005</t>
+          <t>152358</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108037</t>
+          <t>108148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145985</t>
+          <t>147524</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233611</t>
+          <t>230700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290049</t>
+          <t>287850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>55995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192214</t>
+          <t>192614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>228021</t>
+          <t>227036</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>212203</t>
+          <t>213245</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>249664</t>
+          <t>249363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>413180</t>
+          <t>415470</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>463321</t>
+          <t>464484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16742</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70985</t>
+          <t>72430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106698</t>
+          <t>106294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>83404</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>166234</t>
+          <t>168505</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>214736</t>
+          <t>215875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>159923</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>192113</t>
+          <t>190967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>273184</t>
+          <t>273682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>310927</t>
+          <t>309146</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>446579</t>
+          <t>444849</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>494302</t>
+          <t>493232</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74915</t>
+          <t>75912</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51288</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>83631</t>
+          <t>83375</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>104454</t>
+          <t>105057</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>148441</t>
+          <t>148881</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2104605</t>
+          <t>2104221</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2219363</t>
+          <t>2220822</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2250375</t>
+          <t>2252736</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2369772</t>
+          <t>2368984</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4390928</t>
+          <t>4389541</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4557754</t>
+          <t>4560390</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>87160</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>130727</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76675</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>118292</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>177222</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>232053</t>
+          <t>234637</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>967788</t>
+          <t>961210</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1074169</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1005887</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>953120</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1056955</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
           <t>28,3%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>1005887</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>953284</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1065229</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1946023</t>
+          <t>1944460</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2104058</t>
+          <t>2096331</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>117068</t>
+          <t>117374</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>167283</t>
+          <t>166824</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>133591</t>
+          <t>135924</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>184342</t>
+          <t>184531</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>269870</t>
+          <t>266958</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>337742</t>
+          <t>339684</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197575</t>
+          <t>197417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239403</t>
+          <t>239622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183829</t>
+          <t>184527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>224420</t>
+          <t>225477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>397195</t>
+          <t>396505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451782</t>
+          <t>452492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99442</t>
+          <t>102384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138272</t>
+          <t>139803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110181</t>
+          <t>110411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>146317</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>222474</t>
+          <t>220456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>275043</t>
+          <t>273398</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84872</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71565</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>104065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144294</t>
+          <t>144314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277701</t>
+          <t>278744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326588</t>
+          <t>326932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254350</t>
+          <t>252026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300450</t>
+          <t>300439</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545430</t>
+          <t>546322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>610021</t>
+          <t>612485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24202</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152706</t>
+          <t>149904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196059</t>
+          <t>195997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156119</t>
+          <t>157870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197986</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323896</t>
+          <t>323792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385233</t>
+          <t>385189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>115330</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>79215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112886</t>
+          <t>113030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168099</t>
+          <t>169276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>221565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330844</t>
+          <t>328827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>383278</t>
+          <t>384144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>313244</t>
+          <t>312438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>364480</t>
+          <t>364192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659058</t>
+          <t>659262</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>730879</t>
+          <t>730838</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25176</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>48408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180462</t>
+          <t>179205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>230295</t>
+          <t>228281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203781</t>
+          <t>202351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254039</t>
+          <t>251268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394958</t>
+          <t>398138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>462867</t>
+          <t>466782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72139</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109924</t>
+          <t>109632</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>68018</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100037</t>
+          <t>100754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147862</t>
+          <t>148849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>198732</t>
+          <t>197533</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311594</t>
+          <t>311638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>364848</t>
+          <t>364681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>317512</t>
+          <t>318473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>370443</t>
+          <t>370695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>647929</t>
+          <t>645730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>721568</t>
+          <t>724253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30566</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,47 +6146,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>41917</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>28901</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>56867</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>41917</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>30139</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>56151</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162002</t>
+          <t>163731</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211588</t>
+          <t>211950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>172828</t>
+          <t>171418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>221618</t>
+          <t>218061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>349435</t>
+          <t>349993</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417977</t>
+          <t>415200</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82042</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123211</t>
+          <t>124677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162891</t>
+          <t>160935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219370</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216949</t>
+          <t>220443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265342</t>
+          <t>265020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226768</t>
+          <t>228609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275051</t>
+          <t>276140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461915</t>
+          <t>462401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>530355</t>
+          <t>525846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121885</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165870</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137717</t>
+          <t>138212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184125</t>
+          <t>182059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>272905</t>
+          <t>272676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>333854</t>
+          <t>335001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99188</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62425</t>
+          <t>61434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>94658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>133617</t>
+          <t>132240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>180546</t>
+          <t>181991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168491</t>
+          <t>167853</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>204774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>187208</t>
+          <t>184985</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>226896</t>
+          <t>225770</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>365846</t>
+          <t>364695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>418341</t>
+          <t>419485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>104906</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86391</t>
+          <t>85541</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123006</t>
+          <t>124621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170059</t>
+          <t>169871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>219759</t>
+          <t>220169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68375</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>72438</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>92312</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130888</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140369</t>
+          <t>140394</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169556</t>
+          <t>169330</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207232</t>
+          <t>209459</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>252558</t>
+          <t>253492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>357927</t>
+          <t>357320</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413390</t>
+          <t>413161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>41959</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>66090</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82936</t>
+          <t>81661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>125073</t>
+          <t>122324</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>131768</t>
+          <t>132693</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>181675</t>
+          <t>182267</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -7690,12 +7690,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55256</t>
+          <t>54575</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45808</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>77998</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86683</t>
+          <t>84832</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126131</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1737791</t>
+          <t>1741456</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1856233</t>
+          <t>1860158</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1797706</t>
+          <t>1789234</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1912004</t>
+          <t>1913164</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3570685</t>
+          <t>3571319</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3733500</t>
+          <t>3737823</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>115788</t>
+          <t>116207</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>157173</t>
+          <t>156731</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>211025</t>
+          <t>211574</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>913455</t>
+          <t>917657</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1025358</t>
+          <t>1024029</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1037651</t>
+          <t>1035693</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1155967</t>
+          <t>1148130</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1982149</t>
+          <t>1986461</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2144756</t>
+          <t>2142806</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>212558</t>
+          <t>209424</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282811</t>
+          <t>278464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183698</t>
+          <t>183111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230220</t>
+          <t>228019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417602</t>
+          <t>410923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>501029</t>
+          <t>496674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62218</t>
+          <t>62862</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>41764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85652</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -8724,12 +8724,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42627</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>102011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>40427</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77748</t>
+          <t>78942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94978</t>
+          <t>94362</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164341</t>
+          <t>160580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -8837,12 +8837,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75124</t>
+          <t>75149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>13386</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>44576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103317</t>
+          <t>101391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248452</t>
+          <t>247778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298959</t>
+          <t>299703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171964</t>
+          <t>162014</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327053</t>
+          <t>327956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415657</t>
+          <t>409575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>607928</t>
+          <t>608600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>69835</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55962</t>
+          <t>55293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96027</t>
+          <t>98370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>49152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104273</t>
+          <t>105967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121426</t>
+          <t>117824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190067</t>
+          <t>190949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -9293,12 +9293,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37557</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74065</t>
+          <t>75138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270882</t>
+          <t>281895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104576</t>
+          <t>104090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351400</t>
+          <t>357172</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313863</t>
+          <t>312798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>360428</t>
+          <t>358941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>361600</t>
+          <t>361529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>443842</t>
+          <t>447664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>693613</t>
+          <t>689476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>786841</t>
+          <t>784617</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>26884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49642</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61926</t>
+          <t>62579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113297</t>
+          <t>111000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>75826</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122127</t>
+          <t>122850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163097</t>
+          <t>164658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220612</t>
+          <t>221655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54822</t>
+          <t>53277</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83547</t>
+          <t>83962</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70932</t>
+          <t>71640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101648</t>
+          <t>103373</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>146278</t>
+          <t>148660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181141</t>
+          <t>161587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>555733</t>
+          <t>557266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>421605</t>
+          <t>419776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>485849</t>
+          <t>482973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>481844</t>
+          <t>542242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1002759</t>
+          <t>1004826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61818</t>
+          <t>60528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58408</t>
+          <t>58665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>52512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109259</t>
+          <t>112210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180475</t>
+          <t>181535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>655235</t>
+          <t>678412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109758</t>
+          <t>109287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148776</t>
+          <t>148358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>307171</t>
+          <t>306928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>981164</t>
+          <t>901561</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>107936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103698</t>
+          <t>104315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84989</t>
+          <t>102588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>201575</t>
+          <t>199325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352302</t>
+          <t>352028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394353</t>
+          <t>394275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>354452</t>
+          <t>356040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>386201</t>
+          <t>388678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>718633</t>
+          <t>718857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>772418</t>
+          <t>773098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>37433</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>25224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41990</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>49928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>73940</t>
+          <t>74778</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85246</t>
+          <t>86143</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119757</t>
+          <t>123026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68194</t>
+          <t>68493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92630</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>159352</t>
+          <t>162216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204355</t>
+          <t>205742</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -10661,12 +10661,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>41153</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70391</t>
+          <t>68194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50303</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73577</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99408</t>
+          <t>100507</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135257</t>
+          <t>134308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221304</t>
+          <t>220716</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250567</t>
+          <t>251425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>403811</t>
+          <t>403438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>551611</t>
+          <t>555883</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>636957</t>
+          <t>637477</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>853357</t>
+          <t>846737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38063</t>
+          <t>39128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69921</t>
+          <t>68799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>56171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80469</t>
+          <t>80625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>101803</t>
+          <t>99735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11054,12 +11054,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>172093</t>
+          <t>170881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11117,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70763</t>
+          <t>71596</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11167,12 +11167,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>37725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>106069</t>
+          <t>105314</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11202,12 +11202,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -11234,12 +11234,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>183538</t>
+          <t>182916</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>208455</t>
+          <t>207634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>297987</t>
+          <t>297772</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>324092</t>
+          <t>324249</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>490689</t>
+          <t>488733</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>526697</t>
+          <t>525537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11397,47 +11397,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>28146</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>21163</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>36223</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>28146</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>21656</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>37365</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>49593</t>
+          <t>50191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43276</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62429</t>
+          <t>62104</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79701</t>
+          <t>79595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105684</t>
+          <t>106513</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40525</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11588,12 +11588,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59752</t>
+          <t>59089</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11643,12 +11643,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>66586</t>
+          <t>67952</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>93299</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11658,12 +11658,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1562695</t>
+          <t>1609846</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2236086</t>
+          <t>2234310</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2330217</t>
+          <t>2339580</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2672409</t>
+          <t>2679549</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4041784</t>
+          <t>3973335</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4782236</t>
+          <t>4786039</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>238211</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>176683</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>247518</t>
+          <t>242422</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>359613</t>
+          <t>357292</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>465817</t>
+          <t>466268</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>615159</t>
+          <t>616833</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1480020</t>
+          <t>1457534</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>462986</t>
+          <t>462330</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>626384</t>
+          <t>621803</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1172093</t>
+          <t>1155383</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2185682</t>
+          <t>2117910</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>276342</t>
+          <t>287278</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>413108</t>
+          <t>412953</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>363645</t>
+          <t>358684</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>641776</t>
+          <t>652698</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12079,47 +12079,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>805297</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>703072</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>1014943</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>9,82%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>805297</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>703057</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1011512</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D$aparatos-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>257484</t>
+          <t>258060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296457</t>
+          <t>301034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258253</t>
+          <t>257936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296512</t>
+          <t>296540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524961</t>
+          <t>527194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>582917</t>
+          <t>584759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121597</t>
+          <t>118013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>160056</t>
+          <t>158881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>101496</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>137454</t>
+          <t>137877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>234333</t>
+          <t>231747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288904</t>
+          <t>287126</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27971</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>51673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402898</t>
+          <t>401684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454072</t>
+          <t>452492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367068</t>
+          <t>367160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>414577</t>
+          <t>413987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>781386</t>
+          <t>780936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>854100</t>
+          <t>850788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>40878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>30557</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>62983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174644</t>
+          <t>172617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221788</t>
+          <t>222411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160664</t>
+          <t>163239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206308</t>
+          <t>208765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>348118</t>
+          <t>348759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413974</t>
+          <t>416562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>41481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73923</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>396541</t>
+          <t>397524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>451725</t>
+          <t>450879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>403427</t>
+          <t>405748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>455886</t>
+          <t>455596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>818895</t>
+          <t>816562</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>891389</t>
+          <t>889891</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,99%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>53567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184796</t>
+          <t>186776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236222</t>
+          <t>238813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205906</t>
+          <t>205965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256618</t>
+          <t>256492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404738</t>
+          <t>407354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475742</t>
+          <t>479082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42249</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>42701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74739</t>
+          <t>75996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>352675</t>
+          <t>349517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402728</t>
+          <t>400434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371745</t>
+          <t>374397</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>423294</t>
+          <t>423631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>738142</t>
+          <t>739956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>811931</t>
+          <t>810841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>14148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54912</t>
+          <t>55896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166915</t>
+          <t>167429</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>214815</t>
+          <t>216938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153066</t>
+          <t>152918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203566</t>
+          <t>200219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>333757</t>
+          <t>333133</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>401860</t>
+          <t>400967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>40659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36782</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69486</t>
+          <t>69291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248049</t>
+          <t>248945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291275</t>
+          <t>289620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266072</t>
+          <t>267002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308935</t>
+          <t>309749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528999</t>
+          <t>527011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>588715</t>
+          <t>587358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112080</t>
+          <t>112368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152358</t>
+          <t>153642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108148</t>
+          <t>107847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147524</t>
+          <t>146835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230700</t>
+          <t>229806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>287850</t>
+          <t>287386</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31567</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33020</t>
+          <t>31658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55995</t>
+          <t>57204</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192614</t>
+          <t>189671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>227036</t>
+          <t>226326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>213245</t>
+          <t>212539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>249363</t>
+          <t>249231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>415470</t>
+          <t>414718</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>464484</t>
+          <t>465309</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72430</t>
+          <t>72143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106294</t>
+          <t>107091</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>83971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>119776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>168505</t>
+          <t>166574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>215875</t>
+          <t>214411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>35028</t>
+          <t>35954</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>159923</t>
+          <t>160498</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>190967</t>
+          <t>191652</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>273682</t>
+          <t>273750</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>309146</t>
+          <t>311445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>444849</t>
+          <t>446474</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>493232</t>
+          <t>493208</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>74929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>83375</t>
+          <t>84090</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>105057</t>
+          <t>104889</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>148881</t>
+          <t>147244</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37308</t>
+          <t>37963</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>44965</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2104221</t>
+          <t>2095498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2220822</t>
+          <t>2220617</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2252736</t>
+          <t>2254162</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2368984</t>
+          <t>2370938</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4389541</t>
+          <t>4389925</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4560390</t>
+          <t>4545185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>86186</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>130727</t>
+          <t>129469</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>76675</t>
+          <t>75749</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>116826</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>177222</t>
+          <t>177480</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>234637</t>
+          <t>238128</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>961210</t>
+          <t>962831</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1074530</t>
+          <t>1073187</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>953120</t>
+          <t>951445</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1056955</t>
+          <t>1055961</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1944460</t>
+          <t>1950028</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2096331</t>
+          <t>2105918</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>121144</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>166824</t>
+          <t>170593</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>135924</t>
+          <t>135416</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>184531</t>
+          <t>186417</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>266958</t>
+          <t>268301</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>339356</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197417</t>
+          <t>198011</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239622</t>
+          <t>240161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184527</t>
+          <t>185545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225477</t>
+          <t>222911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>396505</t>
+          <t>396317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>452492</t>
+          <t>454888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102384</t>
+          <t>101145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139803</t>
+          <t>142030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110411</t>
+          <t>110354</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146317</t>
+          <t>145957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>220456</t>
+          <t>219812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>273398</t>
+          <t>275106</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84110</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>43453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>70653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104065</t>
+          <t>103698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>144314</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278744</t>
+          <t>278590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326932</t>
+          <t>326436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252026</t>
+          <t>253659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300439</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>546322</t>
+          <t>544148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>612485</t>
+          <t>613535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149904</t>
+          <t>152497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>195997</t>
+          <t>196160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157870</t>
+          <t>157224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200081</t>
+          <t>201432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>323792</t>
+          <t>320742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385189</t>
+          <t>384146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115330</t>
+          <t>117645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113030</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>169276</t>
+          <t>167594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221565</t>
+          <t>218928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>328827</t>
+          <t>330149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>384144</t>
+          <t>382575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312438</t>
+          <t>315435</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>364192</t>
+          <t>365790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659262</t>
+          <t>659887</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>730838</t>
+          <t>733915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>25159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179205</t>
+          <t>179751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228281</t>
+          <t>227016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202351</t>
+          <t>203551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251268</t>
+          <t>251923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398138</t>
+          <t>395420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>466782</t>
+          <t>462316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71924</t>
+          <t>73027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109632</t>
+          <t>108699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68018</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>100073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148849</t>
+          <t>148560</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>197533</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>311638</t>
+          <t>311690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>364681</t>
+          <t>363965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>318473</t>
+          <t>317261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>370695</t>
+          <t>372882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>645730</t>
+          <t>645732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>724253</t>
+          <t>721104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>30974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56867</t>
+          <t>56857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163731</t>
+          <t>164218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211950</t>
+          <t>211200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>171418</t>
+          <t>173595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>218061</t>
+          <t>220955</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>349993</t>
+          <t>353630</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>415200</t>
+          <t>416233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>85452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124677</t>
+          <t>123614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68347</t>
+          <t>69479</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>104107</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160935</t>
+          <t>162613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>213184</t>
+          <t>216347</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220443</t>
+          <t>218866</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265020</t>
+          <t>266389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228609</t>
+          <t>226900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276140</t>
+          <t>275381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>462401</t>
+          <t>465269</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525846</t>
+          <t>528983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20570</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>33899</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124312</t>
+          <t>122448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164608</t>
+          <t>165814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>137258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182059</t>
+          <t>183670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>272676</t>
+          <t>274049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335001</t>
+          <t>332078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62267</t>
+          <t>63096</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>61434</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94658</t>
+          <t>94728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>132147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>181991</t>
+          <t>181869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167853</t>
+          <t>168936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204774</t>
+          <t>204932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>184985</t>
+          <t>187404</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>225770</t>
+          <t>227923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>364695</t>
+          <t>365457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>419485</t>
+          <t>420604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72431</t>
+          <t>72998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105420</t>
+          <t>105672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85541</t>
+          <t>87069</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124621</t>
+          <t>122912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>169871</t>
+          <t>169061</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>220169</t>
+          <t>218712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68375</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72438</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>92312</t>
+          <t>91802</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>130888</t>
+          <t>130030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140394</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169330</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>209459</t>
+          <t>208622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>253492</t>
+          <t>251922</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>357320</t>
+          <t>357604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413161</t>
+          <t>412269</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>42521</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66090</t>
+          <t>66200</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81661</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122324</t>
+          <t>124735</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132693</t>
+          <t>135292</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>182267</t>
+          <t>183338</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -7690,12 +7690,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>54486</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>45568</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>77998</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>85198</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>123415</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1741456</t>
+          <t>1742589</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1860158</t>
+          <t>1859574</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1789234</t>
+          <t>1791631</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1913164</t>
+          <t>1914126</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3571319</t>
+          <t>3566002</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3737823</t>
+          <t>3733767</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>77926</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>116207</t>
+          <t>115937</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>71198</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>108427</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>156731</t>
+          <t>157320</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>211574</t>
+          <t>213105</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>917657</t>
+          <t>916057</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1024029</t>
+          <t>1026634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1035693</t>
+          <t>1041940</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1148130</t>
+          <t>1158477</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1986461</t>
+          <t>1984874</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2142806</t>
+          <t>2142094</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>492038</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>577072</t>
+          <t>577793</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>476803</t>
+          <t>472346</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>562513</t>
+          <t>560787</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>986040</t>
+          <t>995617</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1118529</t>
+          <t>1107542</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>249609</t>
+          <t>255591</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209424</t>
+          <t>225105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>278464</t>
+          <t>286293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8528,32 +8528,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206330</t>
+          <t>237318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183111</t>
+          <t>210407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228019</t>
+          <t>260152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8563,32 +8563,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>455939</t>
+          <t>492910</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>410923</t>
+          <t>450230</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>496674</t>
+          <t>532649</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -8606,102 +8606,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62862</t>
+          <t>46956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>27115</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16826</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41265</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>56772</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>39905</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>77812</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24689</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14979</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38777</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,38%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>61017</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>41764</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>88231</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -8719,32 +8719,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102011</t>
+          <t>101536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8754,32 +8754,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>62098</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78942</t>
+          <t>85123</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8789,32 +8789,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>124673</t>
+          <t>132088</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94362</t>
+          <t>103190</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>160580</t>
+          <t>166598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -8832,32 +8832,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45973</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75149</t>
+          <t>74772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8867,32 +8867,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13386</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>56190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8902,32 +8902,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71394</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>59694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101391</t>
+          <t>118975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -8949,32 +8949,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>274938</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247778</t>
+          <t>278656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299703</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8984,32 +8984,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>316352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162014</t>
+          <t>292944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327956</t>
+          <t>337003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9019,32 +9019,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>551319</t>
+          <t>622278</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409575</t>
+          <t>580503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>608600</t>
+          <t>653451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -9062,32 +9062,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19021</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33147</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9097,32 +9097,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>33330</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46547</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9132,32 +9132,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>55620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>71672</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -9175,32 +9175,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75742</t>
+          <t>80322</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55293</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98370</t>
+          <t>105033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9210,32 +9210,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>84620</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>66503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105967</t>
+          <t>103434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9245,32 +9245,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>157868</t>
+          <t>164943</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117824</t>
+          <t>137571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190949</t>
+          <t>198767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -9288,32 +9288,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>90475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9323,32 +9323,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>65597</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>50920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>82615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9358,32 +9358,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>172808</t>
+          <t>133950</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104090</t>
+          <t>111639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357172</t>
+          <t>163340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -9405,32 +9405,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>336129</t>
+          <t>390215</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>312798</t>
+          <t>365169</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>358941</t>
+          <t>416145</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9440,32 +9440,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>389212</t>
+          <t>388301</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>361529</t>
+          <t>364439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>447664</t>
+          <t>406376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9475,32 +9475,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>725342</t>
+          <t>778515</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>689476</t>
+          <t>743861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>784617</t>
+          <t>810693</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -9518,32 +9518,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>37363</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>51411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>43094</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28918</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53263</t>
+          <t>55500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9588,32 +9588,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77725</t>
+          <t>80457</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62579</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>97289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -9631,32 +9631,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92221</t>
+          <t>102589</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>81433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111000</t>
+          <t>123510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9666,32 +9666,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>103672</t>
+          <t>118093</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>103120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122850</t>
+          <t>138341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9701,32 +9701,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>195893</t>
+          <t>220682</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>193909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221655</t>
+          <t>248063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -9744,32 +9744,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68116</t>
+          <t>86053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>68793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83962</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9779,32 +9779,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57068</t>
+          <t>71990</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71640</t>
+          <t>86753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9814,32 +9814,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>125183</t>
+          <t>158044</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>103373</t>
+          <t>134511</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148660</t>
+          <t>179899</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -9861,32 +9861,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>393115</t>
+          <t>426157</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161587</t>
+          <t>399043</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>557266</t>
+          <t>453756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9896,32 +9896,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>444743</t>
+          <t>444581</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>419776</t>
+          <t>423608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>482973</t>
+          <t>465722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9931,32 +9931,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>837858</t>
+          <t>870738</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>542242</t>
+          <t>836673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1004826</t>
+          <t>902479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -9974,67 +9974,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60528</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>50145</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>41163</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>62136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>6,82%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>47354</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37508</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>58665</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10044,32 +10044,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>92673</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112210</t>
+          <t>110618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -10087,32 +10087,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>382598</t>
+          <t>145659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181535</t>
+          <t>123513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>678412</t>
+          <t>168196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10122,32 +10122,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130006</t>
+          <t>137976</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109287</t>
+          <t>121233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148358</t>
+          <t>155892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10157,32 +10157,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>512604</t>
+          <t>283636</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306928</t>
+          <t>259041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>901561</t>
+          <t>312526</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -10200,32 +10200,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>86273</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107936</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10235,32 +10235,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>102098</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>87378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104315</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10270,32 +10270,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>161044</t>
+          <t>188371</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102588</t>
+          <t>166242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199325</t>
+          <t>212507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -10317,32 +10317,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>372902</t>
+          <t>402108</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352028</t>
+          <t>377565</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394275</t>
+          <t>422665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10352,32 +10352,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>372260</t>
+          <t>406677</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>356040</t>
+          <t>389546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>388678</t>
+          <t>424424</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10387,32 +10387,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>745163</t>
+          <t>808785</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>718857</t>
+          <t>779037</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>773098</t>
+          <t>835016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -10430,32 +10430,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27597</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>21759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10465,32 +10465,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41622</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10500,32 +10500,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>66599</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49928</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>79892</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -10543,32 +10543,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>103379</t>
+          <t>110550</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86143</t>
+          <t>92765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123026</t>
+          <t>129469</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10578,32 +10578,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>79714</t>
+          <t>88244</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>76252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>102686</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10613,32 +10613,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>183093</t>
+          <t>198794</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162216</t>
+          <t>177134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205742</t>
+          <t>223218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -10656,32 +10656,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>65133</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>51732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68194</t>
+          <t>81455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60557</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>61341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>87900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>115909</t>
+          <t>139975</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>121658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>134308</t>
+          <t>161479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -10773,32 +10773,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>236393</t>
+          <t>260548</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>220716</t>
+          <t>241114</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>251425</t>
+          <t>277297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10808,32 +10808,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>477060</t>
+          <t>294612</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>403438</t>
+          <t>280258</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>555883</t>
+          <t>307636</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10843,32 +10843,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>713453</t>
+          <t>555160</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637477</t>
+          <t>529826</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>846737</t>
+          <t>574726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -10886,32 +10886,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>28846</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10921,32 +10921,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>32210</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10956,32 +10956,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>64602</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -10999,32 +10999,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>74741</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56171</t>
+          <t>61809</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80625</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11034,32 +11034,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>63085</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>59755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99735</t>
+          <t>81142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11069,32 +11069,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>144556</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>128548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170881</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -11112,32 +11112,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35526</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>31490</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45689</t>
+          <t>53753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11147,32 +11147,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71596</t>
+          <t>59344</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11182,32 +11182,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>90968</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37725</t>
+          <t>76586</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>105314</t>
+          <t>106728</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -11229,32 +11229,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>195833</t>
+          <t>211888</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182916</t>
+          <t>197503</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>207634</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11264,32 +11264,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>311676</t>
+          <t>335359</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>297772</t>
+          <t>321744</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>324249</t>
+          <t>350538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11299,32 +11299,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>507509</t>
+          <t>547247</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>488733</t>
+          <t>526117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>525537</t>
+          <t>566911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -11342,32 +11342,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11377,27 +11377,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -11412,32 +11412,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>38245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -11455,32 +11455,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>40204</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50191</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11490,32 +11490,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>48918</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62104</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11525,32 +11525,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>92781</t>
+          <t>103519</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79595</t>
+          <t>89235</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106513</t>
+          <t>119015</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -11568,32 +11568,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11603,32 +11603,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>49273</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>46753</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59089</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11638,32 +11638,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>79699</t>
+          <t>93834</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67952</t>
+          <t>79393</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>95761</t>
+          <t>112895</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -11685,32 +11685,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1609846</t>
+          <t>2191626</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2234310</t>
+          <t>2316949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11720,32 +11720,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2339580</t>
+          <t>2370189</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2679549</t>
+          <t>2474243</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11755,32 +11755,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3973335</t>
+          <t>4598997</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4786039</t>
+          <t>4761793</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -11798,32 +11798,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>203541</t>
+          <t>207080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156025</t>
+          <t>181171</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240011</t>
+          <t>236711</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11833,32 +11833,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>214947</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>175549</t>
+          <t>202710</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>242422</t>
+          <t>254958</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11868,32 +11868,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>418488</t>
+          <t>435368</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>357292</t>
+          <t>396060</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>466268</t>
+          <t>475223</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -11911,32 +11911,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>829707</t>
+          <t>628191</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>616833</t>
+          <t>580015</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1457534</t>
+          <t>684328</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11946,32 +11946,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>567939</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>462330</t>
+          <t>579647</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>621803</t>
+          <t>664506</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11981,32 +11981,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1397646</t>
+          <t>1248217</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1155383</t>
+          <t>1185152</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2117910</t>
+          <t>1315414</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -12024,32 +12024,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>287278</t>
+          <t>390405</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>412953</t>
+          <t>476922</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12059,32 +12059,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>358684</t>
+          <t>422255</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>652698</t>
+          <t>496250</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12094,32 +12094,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>703072</t>
+          <t>834312</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1014943</t>
+          <t>949008</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
